--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,6 +54,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -346,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q331"/>
+  <dimension ref="A1:Q332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +575,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -582,7 +650,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -657,7 +725,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -732,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -807,7 +875,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -882,7 +950,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -957,7 +1025,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1100,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1175,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1250,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1325,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1400,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1475,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1550,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1625,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1775,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1850,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1925,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1932,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2075,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2153,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2228,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2303,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2378,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2453,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2528,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2606,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2681,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2759,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2834,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2909,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2987,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2994,7 +3062,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3137,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3215,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3290,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3365,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3443,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3521,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3596,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3674,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3752,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3830,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3908,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3986,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3996,7 +4064,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4139,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4214,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4289,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4364,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4439,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4514,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4589,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4664,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4739,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4814,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4889,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4964,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4971,7 +5039,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5114,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5189,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5264,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5339,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5414,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5489,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5564,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5644,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5724,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5804,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5884,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5964,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5946,7 +6044,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6124,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6204,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6284,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6364,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6444,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6524,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6604,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6684,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6764,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6844,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6924,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6846,7 +7004,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6921,7 +7084,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -6996,7 +7164,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7064,9 +7237,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N89" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7074,7 +7244,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7324,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7404,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7484,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7564,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7644,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7517,9 +7717,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N95" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7527,7 +7724,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7804,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7670,9 +7877,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N97" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7680,7 +7884,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7964,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7830,7 +8044,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7898,9 +8117,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N100" t="n">
-        <v>5.1</v>
-      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7908,7 +8124,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -7983,7 +8204,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8284,12 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8126,9 +8357,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N103" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8136,7 +8364,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8444,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8524,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8354,9 +8597,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N106" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8364,7 +8604,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8432,9 +8677,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N107" t="n">
-        <v>3.8</v>
-      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8442,7 +8684,12 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8764,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8585,9 +8837,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N109" t="n">
-        <v>4</v>
-      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8595,7 +8844,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8663,9 +8917,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N110" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8673,7 +8924,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8741,9 +8997,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N111" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8751,7 +9004,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8819,9 +9077,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N112" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8829,7 +9084,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8897,9 +9157,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N113" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8907,7 +9164,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -8975,9 +9237,6 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N114" t="n">
-        <v>4.3</v>
-      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8985,7 +9244,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9324,12 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9404,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9484,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9564,12 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9644,12 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9724,12 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9804,12 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9884,12 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9964,12 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9735,7 +10044,12 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9810,7 +10124,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9885,7 +10204,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -9960,7 +10284,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10364,12 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10444,12 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10524,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10604,12 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10684,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10764,12 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10805,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -10460,22 +10819,22 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Pobreza</t>
+          <t>Distribución del ingreso</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>pobreza</t>
+          <t>distribucion_del_ingreso</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>SI.POV.DDAY</t>
+          <t>SI.DST.FRST.20</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Pobreza extrema internacional</t>
+          <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10485,7 +10844,12 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10885,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -10560,7 +10924,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10960,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -10635,7 +10999,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10671,7 +11035,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -10710,7 +11074,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10746,7 +11110,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10785,7 +11149,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10821,7 +11185,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -10860,7 +11224,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10896,7 +11260,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -10935,7 +11299,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10971,7 +11335,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -11010,7 +11374,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11410,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -11085,7 +11449,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11485,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11160,7 +11524,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11560,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11235,7 +11599,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11635,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -11310,7 +11674,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11710,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -11385,7 +11749,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11785,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -11460,7 +11824,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11860,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -11535,7 +11899,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11935,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -11610,7 +11974,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11646,7 +12010,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -11685,7 +12049,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11721,7 +12085,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -11760,7 +12124,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11796,7 +12160,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11835,7 +12199,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11871,7 +12235,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -11910,7 +12274,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11946,7 +12310,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -11985,7 +12349,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12385,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -12053,9 +12417,6 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N155" t="n">
-        <v>11.3</v>
-      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12063,7 +12424,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12460,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -12131,6 +12492,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
+      <c r="N156" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12138,7 +12502,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12174,7 +12538,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -12213,7 +12577,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12613,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -12288,7 +12652,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12688,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12363,7 +12727,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12763,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -12438,7 +12802,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12838,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -12506,9 +12870,6 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N161" t="n">
-        <v>12.3</v>
-      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12516,7 +12877,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12913,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -12584,6 +12945,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
+      <c r="N162" t="n">
+        <v>12.3</v>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12591,7 +12955,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12991,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -12659,9 +13023,6 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N163" t="n">
-        <v>7.3</v>
-      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12669,7 +13030,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12705,7 +13066,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -12737,6 +13098,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
+      <c r="N164" t="n">
+        <v>7.3</v>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12744,7 +13108,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12780,7 +13144,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -12819,7 +13183,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12855,7 +13219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -12887,9 +13251,6 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N166" t="n">
-        <v>6.9</v>
-      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12897,7 +13258,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12933,7 +13294,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -12965,6 +13326,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
+      <c r="N167" t="n">
+        <v>6.9</v>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12972,7 +13336,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13372,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -13047,7 +13411,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13447,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -13115,9 +13479,6 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N169" t="n">
-        <v>15.1</v>
-      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13125,7 +13486,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13522,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -13193,6 +13554,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
+      <c r="N170" t="n">
+        <v>15.1</v>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13200,7 +13564,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13236,7 +13600,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -13275,7 +13639,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13675,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -13343,9 +13707,6 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N172" t="n">
-        <v>14.9</v>
-      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13353,7 +13714,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13750,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -13422,7 +13783,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>16.7</v>
+        <v>14.9</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -13431,7 +13792,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13828,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -13499,6 +13860,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
+      <c r="N174" t="n">
+        <v>16.7</v>
+      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13506,7 +13870,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13906,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -13574,9 +13938,6 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N175" t="n">
-        <v>14.7</v>
-      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13584,7 +13945,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13981,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -13653,7 +14014,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>22.1</v>
+        <v>14.7</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -13662,7 +14023,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13698,7 +14059,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -13731,7 +14092,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -13740,7 +14101,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13776,7 +14137,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -13809,7 +14170,7 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>22.8</v>
+        <v>27.1</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -13818,7 +14179,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13854,7 +14215,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -13887,7 +14248,7 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>18.1</v>
+        <v>22.8</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -13896,7 +14257,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13932,7 +14293,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -13965,7 +14326,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>9.699999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -13974,7 +14335,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14371,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -14042,6 +14403,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
+      <c r="N181" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14049,7 +14413,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14085,7 +14449,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -14124,7 +14488,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14524,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -14199,7 +14563,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14599,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -14274,7 +14638,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14310,7 +14674,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -14349,7 +14713,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14749,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -14424,7 +14788,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14824,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -14499,7 +14863,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14899,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -14574,7 +14938,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14974,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -14649,7 +15013,7 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14685,7 +15049,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -14724,7 +15088,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14760,7 +15124,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -14799,7 +15163,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14835,7 +15199,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -14874,7 +15238,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14910,7 +15274,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -14949,7 +15313,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14985,7 +15349,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -15024,7 +15388,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15424,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -15099,7 +15463,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15135,7 +15499,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -15174,7 +15538,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15210,7 +15574,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -15249,7 +15613,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15285,7 +15649,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -15324,7 +15688,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15724,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -15399,7 +15763,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15799,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -15449,22 +15813,22 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Desigualdad</t>
+          <t>Pobreza</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>desigualdad</t>
+          <t>pobreza</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>SI.POV.GINI</t>
+          <t>SI.POV.DDAY</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Índice de Gini</t>
+          <t>Pobreza extrema internacional</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15474,7 +15838,7 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15874,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -15549,7 +15913,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15949,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -15624,7 +15988,7 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15660,7 +16024,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -15699,7 +16063,7 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15735,7 +16099,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -15774,7 +16138,7 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15810,7 +16174,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -15849,7 +16213,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15885,7 +16249,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -15924,7 +16288,7 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15960,7 +16324,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -15999,7 +16363,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16035,7 +16399,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -16074,7 +16438,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16110,7 +16474,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -16149,7 +16513,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16549,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -16224,7 +16588,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16624,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -16299,7 +16663,7 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16699,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -16374,7 +16738,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16774,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -16449,7 +16813,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16849,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -16524,7 +16888,7 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16560,7 +16924,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -16599,7 +16963,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16999,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -16674,7 +17038,7 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16710,7 +17074,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -16749,7 +17113,7 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16785,7 +17149,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -16824,7 +17188,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16860,7 +17224,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -16899,7 +17263,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16935,7 +17299,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -16974,7 +17338,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17010,7 +17374,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -17042,9 +17406,6 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N221" t="n">
-        <v>55.6</v>
-      </c>
       <c r="O221" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17052,7 +17413,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17449,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -17120,6 +17481,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
+      <c r="N222" t="n">
+        <v>55.6</v>
+      </c>
       <c r="O222" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17127,7 +17491,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17527,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -17202,7 +17566,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17602,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -17277,7 +17641,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17313,7 +17677,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -17352,7 +17716,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17388,7 +17752,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -17427,7 +17791,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17463,7 +17827,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -17495,9 +17859,6 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N227" t="n">
-        <v>53.4</v>
-      </c>
       <c r="O227" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17505,7 +17866,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17902,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -17573,6 +17934,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
+      <c r="N228" t="n">
+        <v>53.4</v>
+      </c>
       <c r="O228" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17580,7 +17944,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17616,7 +17980,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -17648,9 +18012,6 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N229" t="n">
-        <v>43.8</v>
-      </c>
       <c r="O229" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17658,7 +18019,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17694,7 +18055,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -17726,6 +18087,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
+      <c r="N230" t="n">
+        <v>43.8</v>
+      </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17733,7 +18097,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17769,7 +18133,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -17808,7 +18172,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17844,7 +18208,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -17876,9 +18240,6 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N232" t="n">
-        <v>42.1</v>
-      </c>
       <c r="O232" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17886,7 +18247,7 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17922,7 +18283,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -17954,6 +18315,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
+      <c r="N233" t="n">
+        <v>42.1</v>
+      </c>
       <c r="O233" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17961,7 +18325,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17997,7 +18361,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -18036,7 +18400,7 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18072,7 +18436,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -18104,9 +18468,6 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N235" t="n">
-        <v>47.2</v>
-      </c>
       <c r="O235" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18114,7 +18475,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18150,7 +18511,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -18182,6 +18543,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
+      <c r="N236" t="n">
+        <v>47.2</v>
+      </c>
       <c r="O236" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18189,7 +18553,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18225,7 +18589,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -18264,7 +18628,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18664,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -18332,9 +18696,6 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N238" t="n">
-        <v>48</v>
-      </c>
       <c r="O238" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18342,7 +18703,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18378,7 +18739,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -18411,7 +18772,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>47.7</v>
+        <v>48</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
@@ -18420,7 +18781,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18817,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -18488,6 +18849,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
+      <c r="N240" t="n">
+        <v>47.7</v>
+      </c>
       <c r="O240" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18495,7 +18859,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18531,7 +18895,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -18563,9 +18927,6 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N241" t="n">
-        <v>47.2</v>
-      </c>
       <c r="O241" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18573,7 +18934,7 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18970,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -18642,7 +19003,7 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -18651,7 +19012,7 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18687,7 +19048,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -18720,7 +19081,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>47.9</v>
+        <v>48.9</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -18729,7 +19090,7 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18765,7 +19126,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -18798,7 +19159,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -18807,7 +19168,7 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18843,7 +19204,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -18876,7 +19237,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>49.3</v>
+        <v>47.3</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -18885,7 +19246,7 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18921,7 +19282,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -18954,7 +19315,7 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>44.7</v>
+        <v>49.3</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -18963,7 +19324,7 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18999,7 +19360,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -19031,6 +19392,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
+      <c r="N247" t="n">
+        <v>44.7</v>
+      </c>
       <c r="O247" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19038,7 +19402,7 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19438,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -19113,7 +19477,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19513,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -19188,7 +19552,7 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19224,7 +19588,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -19263,7 +19627,7 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19663,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -19338,7 +19702,7 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19374,7 +19738,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -19413,7 +19777,7 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19449,7 +19813,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -19488,7 +19852,7 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19888,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -19563,7 +19927,7 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19599,7 +19963,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -19638,7 +20002,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19674,7 +20038,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -19713,7 +20077,7 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19749,7 +20113,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -19788,7 +20152,7 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19824,7 +20188,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -19863,7 +20227,7 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19899,7 +20263,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -19938,7 +20302,7 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19974,7 +20338,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -20013,7 +20377,7 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20049,7 +20413,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -20088,7 +20452,7 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20124,7 +20488,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -20163,7 +20527,7 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20563,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -20238,7 +20602,7 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20638,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -20313,7 +20677,7 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20349,7 +20713,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -20388,7 +20752,7 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20788,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -20438,22 +20802,22 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Pobreza</t>
+          <t>Desigualdad</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>pobreza</t>
+          <t>desigualdad</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>SI.POV.NAHC</t>
+          <t>SI.POV.GINI</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Pobreza según línea nacional</t>
+          <t>Índice de Gini</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20463,7 +20827,7 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20499,7 +20863,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -20538,7 +20902,7 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20938,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -20613,7 +20977,7 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20649,7 +21013,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -20688,7 +21052,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20724,7 +21088,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -20763,7 +21127,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20799,7 +21163,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -20838,7 +21202,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20874,7 +21238,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -20913,7 +21277,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20949,7 +21313,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -20988,7 +21352,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21024,7 +21388,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -21063,7 +21427,7 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21463,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -21138,7 +21502,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21538,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -21213,7 +21577,7 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21249,7 +21613,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -21288,7 +21652,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21324,7 +21688,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -21363,7 +21727,7 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21763,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -21438,7 +21802,7 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21474,7 +21838,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -21513,7 +21877,7 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21549,7 +21913,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -21588,7 +21952,7 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21624,7 +21988,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -21663,7 +22027,7 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21699,7 +22063,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -21738,7 +22102,7 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21774,7 +22138,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -21813,7 +22177,7 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21849,7 +22213,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -21888,7 +22252,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21924,7 +22288,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -21963,7 +22327,7 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21999,7 +22363,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -22038,7 +22402,7 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22074,7 +22438,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -22113,7 +22477,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22513,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -22188,7 +22552,7 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22224,7 +22588,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -22263,7 +22627,7 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22299,7 +22663,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -22338,7 +22702,7 @@
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22738,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -22413,7 +22777,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22813,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -22488,7 +22852,7 @@
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22888,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -22563,7 +22927,7 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22599,7 +22963,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -22638,7 +23002,7 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22674,7 +23038,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -22713,7 +23077,7 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22749,7 +23113,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -22788,7 +23152,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22824,7 +23188,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -22863,7 +23227,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22899,7 +23263,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -22938,7 +23302,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22974,7 +23338,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -23013,7 +23377,7 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23049,7 +23413,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -23088,7 +23452,7 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23488,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -23163,7 +23527,7 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23199,7 +23563,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -23231,9 +23595,6 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N303" t="n">
-        <v>55.6</v>
-      </c>
       <c r="O303" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23241,7 +23602,7 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23277,7 +23638,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -23310,7 +23671,7 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>49</v>
+        <v>55.6</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -23319,7 +23680,7 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23355,7 +23716,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -23388,7 +23749,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>42.8</v>
+        <v>49</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -23397,7 +23758,7 @@
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23433,7 +23794,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -23466,7 +23827,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>41.6</v>
+        <v>42.8</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -23475,7 +23836,7 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23872,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -23544,7 +23905,7 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>31.1</v>
+        <v>41.6</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -23553,7 +23914,7 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23589,7 +23950,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -23622,7 +23983,7 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>41.1</v>
+        <v>31.1</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -23631,7 +23992,7 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23667,7 +24028,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -23700,7 +24061,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>54</v>
+        <v>41.1</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -23709,7 +24070,7 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23745,7 +24106,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -23778,7 +24139,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>53.1</v>
+        <v>54</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -23787,7 +24148,7 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23823,7 +24184,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -23856,7 +24217,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>42.4</v>
+        <v>53.1</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -23865,7 +24226,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23901,7 +24262,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -23934,7 +24295,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>33.1</v>
+        <v>42.4</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -23943,7 +24304,7 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23979,7 +24340,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -24012,7 +24373,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>27.5</v>
+        <v>33.1</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -24021,7 +24382,7 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24057,7 +24418,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -24090,7 +24451,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -24099,7 +24460,7 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24135,7 +24496,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -24168,7 +24529,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>26.4</v>
+        <v>27.7</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -24177,7 +24538,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24213,7 +24574,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -24246,7 +24607,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -24255,7 +24616,7 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24291,7 +24652,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -24324,7 +24685,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>27.4</v>
+        <v>26.8</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -24333,7 +24694,7 @@
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24369,7 +24730,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -24402,7 +24763,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -24411,7 +24772,7 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24447,7 +24808,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -24480,7 +24841,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>29.4</v>
+        <v>27.2</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -24489,7 +24850,7 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24525,7 +24886,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -24558,7 +24919,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -24567,7 +24928,7 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24603,7 +24964,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -24636,7 +24997,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>33.1</v>
+        <v>29.5</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -24645,7 +25006,7 @@
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24681,7 +25042,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -24713,6 +25074,9 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
+      <c r="N322" t="n">
+        <v>33.1</v>
+      </c>
       <c r="O322" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24720,7 +25084,7 @@
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24756,7 +25120,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -24795,7 +25159,7 @@
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24831,7 +25195,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -24870,7 +25234,7 @@
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24906,7 +25270,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -24945,7 +25309,7 @@
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24981,7 +25345,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -25020,7 +25384,7 @@
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25420,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -25095,7 +25459,7 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25495,7 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -25170,7 +25534,7 @@
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25206,7 +25570,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -25245,7 +25609,7 @@
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25645,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -25320,7 +25684,7 @@
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25356,46 +25720,121 @@
         </is>
       </c>
       <c r="G331" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Pobreza y desigualdad</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>pobreza_y_desigualdad</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>pobreza</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>SI.POV.NAHC</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Pobreza según línea nacional</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
         <v>2025</v>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>Pobreza y desigualdad</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>pobreza_y_desigualdad</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Pobreza y desigualdad</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>pobreza_y_desigualdad</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
         <is>
           <t>Pobreza</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="K332" t="inlineStr">
         <is>
           <t>pobreza</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="L332" t="inlineStr">
         <is>
           <t>SI.POV.NAHC</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="M332" t="inlineStr">
         <is>
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="O331" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25445,7 +25884,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25466,7 +25905,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -674,7 +689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -751,7 +766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -828,7 +843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -905,7 +920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -982,7 +997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1059,7 +1074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1136,7 +1151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1213,7 +1228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1290,7 +1305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1367,7 +1382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1444,7 +1459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1521,7 +1536,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1598,7 +1613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1675,7 +1690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1752,7 +1767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1829,7 +1844,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1906,7 +1921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1983,7 +1998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2060,7 +2075,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2137,7 +2152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2214,7 +2229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2247,7 +2262,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="8" t="n">
         <v>59.9</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2293,7 +2308,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2370,7 +2385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2447,7 +2462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2524,7 +2539,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2601,7 +2616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2678,7 +2693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2711,7 +2726,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="7" t="n">
         <v>58</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2757,7 +2772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2834,7 +2849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2867,7 +2882,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="8" t="n">
         <v>48.7</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2913,7 +2928,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2990,7 +3005,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3067,7 +3082,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3100,7 +3115,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="8" t="n">
         <v>47.7</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3146,7 +3161,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3223,7 +3238,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3300,7 +3315,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3333,7 +3348,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="8" t="n">
         <v>51.9</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3379,7 +3394,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3456,7 +3471,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3533,7 +3548,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3566,7 +3581,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="8" t="n">
         <v>52.5</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3612,7 +3627,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3645,7 +3660,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="8" t="n">
         <v>52.3</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3691,7 +3706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3768,7 +3783,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3801,7 +3816,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="8" t="n">
         <v>51.9</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3847,7 +3862,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3880,7 +3895,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="8" t="n">
         <v>53.1</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3926,7 +3941,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3959,7 +3974,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="7" t="n">
         <v>52</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4005,7 +4020,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4038,7 +4053,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="8" t="n">
         <v>51.5</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4084,7 +4099,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4117,7 +4132,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="8" t="n">
         <v>52.9</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4163,7 +4178,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4196,7 +4211,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="8" t="n">
         <v>49.5</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4242,7 +4257,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4319,7 +4334,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4396,7 +4411,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4473,7 +4488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4550,7 +4565,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4627,7 +4642,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4704,7 +4719,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4781,7 +4796,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4858,7 +4873,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4935,7 +4950,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5012,7 +5027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5089,7 +5104,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5166,7 +5181,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5243,7 +5258,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5320,7 +5335,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5397,7 +5412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5474,7 +5489,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5551,7 +5566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5628,7 +5643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5705,7 +5720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5786,7 +5801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5867,7 +5882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5948,7 +5963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6029,7 +6044,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6110,7 +6125,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6191,7 +6206,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6272,7 +6287,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6353,7 +6368,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6434,7 +6449,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6515,7 +6530,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6596,7 +6611,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6677,7 +6692,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6758,7 +6773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6839,7 +6854,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6920,7 +6935,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7001,7 +7016,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7082,7 +7097,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7163,7 +7178,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7244,7 +7259,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7325,7 +7340,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7406,7 +7421,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7487,7 +7502,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7568,7 +7583,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7649,7 +7664,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7730,7 +7745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7811,7 +7826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7892,7 +7907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7973,7 +7988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8054,7 +8069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8135,7 +8150,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8216,7 +8231,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8297,7 +8312,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8378,7 +8393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8459,7 +8474,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8540,7 +8555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8621,7 +8636,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8702,7 +8717,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8783,7 +8798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8864,7 +8879,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8945,7 +8960,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9026,7 +9041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9107,7 +9122,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9188,7 +9203,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9269,7 +9284,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9350,7 +9365,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9431,7 +9446,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9512,7 +9527,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9593,7 +9608,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9674,7 +9689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9755,7 +9770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9836,7 +9851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9917,7 +9932,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -9998,7 +10013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10079,7 +10094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10160,7 +10175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10241,7 +10256,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10322,7 +10337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10403,7 +10418,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10484,7 +10499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10565,7 +10580,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10646,7 +10661,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10727,7 +10742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10808,7 +10823,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10889,7 +10904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10970,7 +10985,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11051,7 +11066,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11132,7 +11147,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11209,7 +11224,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11286,7 +11301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11363,7 +11378,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11440,7 +11455,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11517,7 +11532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11594,7 +11609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11671,7 +11686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11748,7 +11763,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11825,7 +11840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11902,7 +11917,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -11979,7 +11994,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12056,7 +12071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12133,7 +12148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12210,7 +12225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12287,7 +12302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12364,7 +12379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12441,7 +12456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12518,7 +12533,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12595,7 +12610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12672,7 +12687,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12749,7 +12764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12782,7 +12797,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N161" s="4" t="n">
+      <c r="N161" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="O161" s="4" t="inlineStr">
@@ -12828,7 +12843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12905,7 +12920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -12982,7 +12997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13059,7 +13074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13136,7 +13151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13213,7 +13228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13246,7 +13261,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N167" s="4" t="n">
+      <c r="N167" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="O167" s="4" t="inlineStr">
@@ -13292,7 +13307,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13369,7 +13384,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13402,7 +13417,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N169" s="4" t="n">
+      <c r="N169" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="O169" s="4" t="inlineStr">
@@ -13448,7 +13463,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13525,7 +13540,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13602,7 +13617,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13635,7 +13650,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N172" s="4" t="n">
+      <c r="N172" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
@@ -13681,7 +13696,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13758,7 +13773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13835,7 +13850,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -13868,7 +13883,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N175" s="4" t="n">
+      <c r="N175" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
@@ -13914,7 +13929,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -13991,7 +14006,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14068,7 +14083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14101,7 +14116,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N178" s="4" t="n">
+      <c r="N178" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
@@ -14147,7 +14162,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14180,7 +14195,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N179" s="4" t="n">
+      <c r="N179" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
@@ -14226,7 +14241,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14303,7 +14318,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14336,7 +14351,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N181" s="4" t="n">
+      <c r="N181" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
@@ -14382,7 +14397,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14415,7 +14430,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N182" s="4" t="n">
+      <c r="N182" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
@@ -14461,7 +14476,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14494,7 +14509,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N183" s="4" t="n">
+      <c r="N183" s="8" t="n">
         <v>27.1</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
@@ -14540,7 +14555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14573,7 +14588,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N184" s="4" t="n">
+      <c r="N184" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
@@ -14619,7 +14634,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14652,7 +14667,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N185" s="4" t="n">
+      <c r="N185" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
@@ -14698,7 +14713,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14731,7 +14746,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N186" s="4" t="n">
+      <c r="N186" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
@@ -14777,7 +14792,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -14854,7 +14869,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14931,7 +14946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15008,7 +15023,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15085,7 +15100,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15162,7 +15177,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15239,7 +15254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15316,7 +15331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15393,7 +15408,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15470,7 +15485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15547,7 +15562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15624,7 +15639,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15701,7 +15716,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15778,7 +15793,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -15855,7 +15870,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -15932,7 +15947,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16009,7 +16024,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16086,7 +16101,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16163,7 +16178,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16240,7 +16255,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16317,7 +16332,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16394,7 +16409,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16471,7 +16486,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16548,7 +16563,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16625,7 +16640,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16702,7 +16717,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16779,7 +16794,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -16856,7 +16871,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -16933,7 +16948,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17010,7 +17025,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17087,7 +17102,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17164,7 +17179,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17241,7 +17256,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17318,7 +17333,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17395,7 +17410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17472,7 +17487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17549,7 +17564,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17626,7 +17641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -17703,7 +17718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -17780,7 +17795,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -17857,7 +17872,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -17890,7 +17905,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N227" s="4" t="n">
+      <c r="N227" s="8" t="n">
         <v>55.6</v>
       </c>
       <c r="O227" s="4" t="inlineStr">
@@ -17936,7 +17951,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18013,7 +18028,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18090,7 +18105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18167,7 +18182,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18244,7 +18259,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18321,7 +18336,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18354,7 +18369,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N233" s="4" t="n">
+      <c r="N233" s="8" t="n">
         <v>53.4</v>
       </c>
       <c r="O233" s="4" t="inlineStr">
@@ -18400,7 +18415,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18477,7 +18492,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18510,7 +18525,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n">
+      <c r="N235" s="8" t="n">
         <v>43.8</v>
       </c>
       <c r="O235" s="4" t="inlineStr">
@@ -18556,7 +18571,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18633,7 +18648,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -18710,7 +18725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -18743,7 +18758,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n">
+      <c r="N238" s="8" t="n">
         <v>42.1</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
@@ -18789,7 +18804,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -18866,7 +18881,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -18943,7 +18958,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -18976,7 +18991,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N241" s="4" t="n">
+      <c r="N241" s="8" t="n">
         <v>47.2</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
@@ -19022,7 +19037,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19099,7 +19114,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19176,7 +19191,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19209,7 +19224,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n">
+      <c r="N244" s="7" t="n">
         <v>48</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
@@ -19255,7 +19270,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19288,7 +19303,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N245" s="4" t="n">
+      <c r="N245" s="8" t="n">
         <v>47.7</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
@@ -19334,7 +19349,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19411,7 +19426,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19444,7 +19459,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N247" s="4" t="n">
+      <c r="N247" s="8" t="n">
         <v>47.2</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
@@ -19490,7 +19505,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19523,7 +19538,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n">
+      <c r="N248" s="8" t="n">
         <v>48.9</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
@@ -19569,7 +19584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -19602,7 +19617,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N249" s="4" t="n">
+      <c r="N249" s="8" t="n">
         <v>47.9</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
@@ -19648,7 +19663,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -19681,7 +19696,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n">
+      <c r="N250" s="8" t="n">
         <v>47.3</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
@@ -19727,7 +19742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -19760,7 +19775,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N251" s="4" t="n">
+      <c r="N251" s="8" t="n">
         <v>49.3</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
@@ -19806,7 +19821,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -19839,7 +19854,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n">
+      <c r="N252" s="8" t="n">
         <v>44.7</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
@@ -19885,7 +19900,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -19962,7 +19977,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20039,7 +20054,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20116,7 +20131,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20193,7 +20208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20270,7 +20285,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20347,7 +20362,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20424,7 +20439,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20501,7 +20516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -20578,7 +20593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -20655,7 +20670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -20732,7 +20747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -20809,7 +20824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -20886,7 +20901,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -20963,7 +20978,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21040,7 +21055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21117,7 +21132,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21194,7 +21209,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21271,7 +21286,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -21348,7 +21363,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -21425,7 +21440,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -21502,7 +21517,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -21579,7 +21594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -21656,7 +21671,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -21733,7 +21748,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -21810,7 +21825,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -21887,7 +21902,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -21964,7 +21979,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22041,7 +22056,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22118,7 +22133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22195,7 +22210,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22272,7 +22287,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -22349,7 +22364,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -22426,7 +22441,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -22503,7 +22518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -22580,7 +22595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -22657,7 +22672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -22734,7 +22749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -22811,7 +22826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -22888,7 +22903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -22965,7 +22980,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23042,7 +23057,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23119,7 +23134,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23196,7 +23211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23273,7 +23288,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -23350,7 +23365,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -23427,7 +23442,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -23504,7 +23519,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -23581,7 +23596,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -23658,7 +23673,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -23735,7 +23750,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -23812,7 +23827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -23889,7 +23904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -23966,7 +23981,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24043,7 +24058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24120,7 +24135,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24197,7 +24212,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -24230,7 +24245,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n">
+      <c r="N309" s="8" t="n">
         <v>55.6</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
@@ -24276,7 +24291,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -24309,7 +24324,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n">
+      <c r="N310" s="7" t="n">
         <v>49</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
@@ -24355,7 +24370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -24388,7 +24403,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n">
+      <c r="N311" s="8" t="n">
         <v>42.8</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
@@ -24434,7 +24449,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -24467,7 +24482,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n">
+      <c r="N312" s="8" t="n">
         <v>41.6</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
@@ -24513,7 +24528,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -24546,7 +24561,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n">
+      <c r="N313" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
@@ -24592,7 +24607,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -24625,7 +24640,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n">
+      <c r="N314" s="8" t="n">
         <v>41.1</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
@@ -24671,7 +24686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -24704,7 +24719,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n">
+      <c r="N315" s="7" t="n">
         <v>54</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
@@ -24750,7 +24765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -24783,7 +24798,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n">
+      <c r="N316" s="8" t="n">
         <v>53.1</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
@@ -24829,7 +24844,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -24862,7 +24877,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n">
+      <c r="N317" s="8" t="n">
         <v>42.4</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
@@ -24908,7 +24923,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -24941,7 +24956,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n">
+      <c r="N318" s="8" t="n">
         <v>33.1</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
@@ -24987,7 +25002,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25020,7 +25035,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n">
+      <c r="N319" s="8" t="n">
         <v>27.5</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
@@ -25066,7 +25081,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25099,7 +25114,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n">
+      <c r="N320" s="8" t="n">
         <v>27.7</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
@@ -25145,7 +25160,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25178,7 +25193,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n">
+      <c r="N321" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
@@ -25224,7 +25239,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -25257,7 +25272,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n">
+      <c r="N322" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
@@ -25303,7 +25318,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -25336,7 +25351,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n">
+      <c r="N323" s="8" t="n">
         <v>27.4</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
@@ -25382,7 +25397,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -25415,7 +25430,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n">
+      <c r="N324" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
@@ -25461,7 +25476,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -25494,7 +25509,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n">
+      <c r="N325" s="8" t="n">
         <v>29.4</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
@@ -25540,7 +25555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -25573,7 +25588,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n">
+      <c r="N326" s="8" t="n">
         <v>29.5</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
@@ -25619,7 +25634,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -25652,7 +25667,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n">
+      <c r="N327" s="8" t="n">
         <v>33.1</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
@@ -25698,7 +25713,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -25775,7 +25790,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -25852,7 +25867,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -25929,7 +25944,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26006,7 +26021,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -26083,7 +26098,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26160,7 +26175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -26237,7 +26252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -26314,7 +26329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -26391,7 +26406,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -26527,7 +26542,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -26537,7 +26552,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>331</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,26 +82,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,16 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -134,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -149,16 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -455,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -480,14 +542,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Pobreza y desigualdad</t>
+          <t>Banco Mundial - Pobreza y desigualdad</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>World Development Indicators</t>
+          <t>Venezuela</t>
         </is>
       </c>
     </row>
@@ -612,7 +674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -653,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -689,7 +751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -730,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -766,7 +828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -807,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -843,7 +905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -884,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -920,7 +982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -961,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -997,7 +1059,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1038,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1074,7 +1136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1115,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1151,7 +1213,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1192,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1228,7 +1290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1269,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1305,7 +1367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1346,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1382,7 +1444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1423,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1459,7 +1521,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1500,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1536,7 +1598,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1577,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1613,7 +1675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1654,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1690,7 +1752,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1731,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1767,7 +1829,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1808,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1844,7 +1906,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1885,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -1921,7 +1983,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1962,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -1998,7 +2060,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2039,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2075,7 +2137,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2116,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2152,7 +2214,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2193,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2229,7 +2291,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2262,7 +2324,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="N28" s="6" t="n">
         <v>59.9</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2272,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2308,7 +2370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2349,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2385,7 +2447,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2426,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2462,7 +2524,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2503,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2539,7 +2601,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2580,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2616,7 +2678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2657,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2693,7 +2755,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2726,7 +2788,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N34" s="7" t="n">
+      <c r="N34" s="5" t="n">
         <v>58</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2736,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2772,7 +2834,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2813,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2849,7 +2911,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2882,7 +2944,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="6" t="n">
         <v>48.7</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2892,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -2928,7 +2990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2969,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3005,7 +3067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3046,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3082,7 +3144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3115,7 +3177,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="6" t="n">
         <v>47.7</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3125,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3161,7 +3223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3202,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3238,7 +3300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3279,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3315,7 +3377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3348,7 +3410,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="6" t="n">
         <v>51.9</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3358,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3394,7 +3456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3435,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3471,7 +3533,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3512,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3548,7 +3610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3581,7 +3643,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N45" s="8" t="n">
+      <c r="N45" s="6" t="n">
         <v>52.5</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3591,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3627,7 +3689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3660,7 +3722,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N46" s="8" t="n">
+      <c r="N46" s="6" t="n">
         <v>52.3</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3670,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3706,7 +3768,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3747,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3783,7 +3845,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3816,7 +3878,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N48" s="8" t="n">
+      <c r="N48" s="6" t="n">
         <v>51.9</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3826,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3862,7 +3924,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3895,7 +3957,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N49" s="8" t="n">
+      <c r="N49" s="6" t="n">
         <v>53.1</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3905,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -3941,7 +4003,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3974,7 +4036,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N50" s="7" t="n">
+      <c r="N50" s="5" t="n">
         <v>52</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -3984,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4020,7 +4082,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4053,7 +4115,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N51" s="8" t="n">
+      <c r="N51" s="6" t="n">
         <v>51.5</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4063,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4099,7 +4161,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4132,7 +4194,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N52" s="8" t="n">
+      <c r="N52" s="6" t="n">
         <v>52.9</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4142,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4178,7 +4240,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4211,7 +4273,7 @@
           <t>Participación del 20 por ciento más rico en el ingreso</t>
         </is>
       </c>
-      <c r="N53" s="8" t="n">
+      <c r="N53" s="6" t="n">
         <v>49.5</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4221,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4257,7 +4319,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4298,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4334,7 +4396,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G55" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4375,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4411,7 +4473,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4452,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4488,7 +4550,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4529,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4565,7 +4627,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4606,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4642,7 +4704,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4683,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4719,7 +4781,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4760,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4796,7 +4858,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="G61" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4837,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4873,7 +4935,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4914,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -4950,7 +5012,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -4991,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5027,7 +5089,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5068,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5104,7 +5166,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5145,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5181,7 +5243,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5222,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5258,7 +5320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5299,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5335,7 +5397,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5376,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5412,7 +5474,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5453,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5489,7 +5551,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G70" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5530,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5566,7 +5628,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5607,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5643,7 +5705,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5684,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5720,7 +5782,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="G73" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5761,14 +5823,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5801,7 +5859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5842,14 +5900,10 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5882,7 +5936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="7" t="n">
+      <c r="G75" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5923,14 +5977,10 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -5963,7 +6013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="7" t="n">
+      <c r="G76" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6004,14 +6054,10 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -6044,7 +6090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n">
+      <c r="G77" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6085,14 +6131,10 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -6125,7 +6167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n">
+      <c r="G78" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6166,14 +6208,10 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6206,7 +6244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n">
+      <c r="G79" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6247,14 +6285,10 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -6287,7 +6321,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n">
+      <c r="G80" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6328,14 +6362,10 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6368,7 +6398,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="7" t="n">
+      <c r="G81" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6409,14 +6439,10 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6449,7 +6475,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n">
+      <c r="G82" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6490,14 +6516,10 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6530,7 +6552,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6571,14 +6593,10 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6611,7 +6629,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6652,14 +6670,10 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6692,7 +6706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6733,14 +6747,10 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6773,7 +6783,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="7" t="n">
+      <c r="G86" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6814,14 +6824,10 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -6854,7 +6860,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="7" t="n">
+      <c r="G87" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6895,14 +6901,10 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q87" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -6935,7 +6937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n">
+      <c r="G88" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6976,14 +6978,10 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7016,7 +7014,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="G89" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7057,14 +7055,10 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7097,7 +7091,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n">
+      <c r="G90" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7138,14 +7132,10 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7178,7 +7168,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
+      <c r="G91" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7219,14 +7209,10 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7259,7 +7245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
+      <c r="G92" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7300,14 +7286,10 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q92" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -7340,7 +7322,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n">
+      <c r="G93" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7381,14 +7363,10 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -7421,7 +7399,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
+      <c r="G94" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7454,7 +7432,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N94" s="4" t="n"/>
+      <c r="N94" s="6" t="n">
+        <v>3.1</v>
+      </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7462,14 +7442,10 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -7502,7 +7478,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
+      <c r="G95" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7543,14 +7519,10 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -7583,7 +7555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
+      <c r="G96" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7624,14 +7596,10 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7664,7 +7632,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n">
+      <c r="G97" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7705,14 +7673,10 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -7745,7 +7709,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="7" t="n">
+      <c r="G98" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7786,14 +7750,10 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -7826,7 +7786,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="7" t="n">
+      <c r="G99" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7867,14 +7827,10 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -7907,7 +7863,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="7" t="n">
+      <c r="G100" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7940,7 +7896,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N100" s="4" t="n"/>
+      <c r="N100" s="6" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7948,14 +7906,10 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -7988,7 +7942,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="7" t="n">
+      <c r="G101" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8029,14 +7983,10 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -8069,7 +8019,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="7" t="n">
+      <c r="G102" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8102,7 +8052,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N102" s="4" t="n"/>
+      <c r="N102" s="6" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8110,14 +8062,10 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8150,7 +8098,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="7" t="n">
+      <c r="G103" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8191,14 +8139,10 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -8231,7 +8175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="7" t="n">
+      <c r="G104" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8272,14 +8216,10 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -8312,7 +8252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="G105" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8345,7 +8285,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n"/>
+      <c r="N105" s="6" t="n">
+        <v>5.1</v>
+      </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8353,14 +8295,10 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -8393,7 +8331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="7" t="n">
+      <c r="G106" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8434,14 +8372,10 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -8474,7 +8408,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n">
+      <c r="G107" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8515,14 +8449,10 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -8555,7 +8485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n">
+      <c r="G108" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8588,7 +8518,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N108" s="4" t="n"/>
+      <c r="N108" s="6" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8596,14 +8528,10 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -8636,7 +8564,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="G109" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8677,14 +8605,10 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -8717,7 +8641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="G110" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8758,14 +8682,10 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -8798,7 +8718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="7" t="n">
+      <c r="G111" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8831,7 +8751,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N111" s="4" t="n"/>
+      <c r="N111" s="6" t="n">
+        <v>3.7</v>
+      </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8839,14 +8761,10 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -8879,7 +8797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="7" t="n">
+      <c r="G112" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8912,7 +8830,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N112" s="4" t="n"/>
+      <c r="N112" s="6" t="n">
+        <v>3.8</v>
+      </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8920,14 +8840,10 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q112" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -8960,7 +8876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="7" t="n">
+      <c r="G113" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9001,14 +8917,10 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -9041,7 +8953,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="7" t="n">
+      <c r="G114" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9074,7 +8986,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N114" s="4" t="n"/>
+      <c r="N114" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9082,14 +8996,10 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -9122,7 +9032,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="7" t="n">
+      <c r="G115" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9155,7 +9065,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N115" s="4" t="n"/>
+      <c r="N115" s="6" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9163,14 +9075,10 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -9203,7 +9111,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="7" t="n">
+      <c r="G116" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9236,7 +9144,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N116" s="4" t="n"/>
+      <c r="N116" s="6" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9244,14 +9154,10 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9284,7 +9190,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="7" t="n">
+      <c r="G117" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9317,7 +9223,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N117" s="4" t="n"/>
+      <c r="N117" s="6" t="n">
+        <v>3.5</v>
+      </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9325,14 +9233,10 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9365,7 +9269,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="7" t="n">
+      <c r="G118" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9398,7 +9302,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N118" s="4" t="n"/>
+      <c r="N118" s="6" t="n">
+        <v>2.9</v>
+      </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9406,14 +9312,10 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q118" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -9446,7 +9348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="7" t="n">
+      <c r="G119" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9479,7 +9381,9 @@
           <t>Participación del 20 por ciento más pobre en el ingreso</t>
         </is>
       </c>
-      <c r="N119" s="4" t="n"/>
+      <c r="N119" s="6" t="n">
+        <v>4.3</v>
+      </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9487,14 +9391,10 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -9527,7 +9427,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n">
+      <c r="G120" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9568,14 +9468,10 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -9608,7 +9504,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="7" t="n">
+      <c r="G121" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9649,14 +9545,10 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -9689,7 +9581,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="7" t="n">
+      <c r="G122" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9730,14 +9622,10 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -9770,7 +9658,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="7" t="n">
+      <c r="G123" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9811,14 +9699,10 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -9851,7 +9735,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="7" t="n">
+      <c r="G124" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9892,14 +9776,10 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -9932,7 +9812,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n">
+      <c r="G125" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -9973,14 +9853,10 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -10013,7 +9889,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="7" t="n">
+      <c r="G126" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10054,14 +9930,10 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q126" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -10094,7 +9966,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="7" t="n">
+      <c r="G127" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10135,14 +10007,10 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -10175,7 +10043,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n">
+      <c r="G128" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10216,14 +10084,10 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -10256,7 +10120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="7" t="n">
+      <c r="G129" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10297,14 +10161,10 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -10337,7 +10197,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="7" t="n">
+      <c r="G130" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10378,14 +10238,10 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -10418,7 +10274,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="7" t="n">
+      <c r="G131" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10459,14 +10315,10 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -10499,7 +10351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="7" t="n">
+      <c r="G132" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10540,14 +10392,10 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10580,7 +10428,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="7" t="n">
+      <c r="G133" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10621,14 +10469,10 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q133" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -10661,7 +10505,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="7" t="n">
+      <c r="G134" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10702,14 +10546,10 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10742,7 +10582,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="7" t="n">
+      <c r="G135" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10783,14 +10623,10 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -10823,7 +10659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="7" t="n">
+      <c r="G136" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10864,14 +10700,10 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -10904,7 +10736,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="7" t="n">
+      <c r="G137" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10945,14 +10777,10 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q137" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -10985,7 +10813,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="7" t="n">
+      <c r="G138" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11026,14 +10854,10 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -11066,8 +10890,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="7" t="n">
-        <v>2026</v>
+      <c r="G139" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11081,22 +10905,22 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Distribución del ingreso</t>
+          <t>Pobreza</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>distribucion_del_ingreso</t>
+          <t>pobreza</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>SI.DST.FRST.20</t>
+          <t>SI.POV.DDAY</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Participación del 20 por ciento más pobre en el ingreso</t>
+          <t>Pobreza extrema internacional</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11107,14 +10931,10 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -11147,8 +10967,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="7" t="n">
-        <v>1960</v>
+      <c r="G140" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11188,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11224,8 +11044,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="7" t="n">
-        <v>1961</v>
+      <c r="G141" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11265,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11301,8 +11121,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="7" t="n">
-        <v>1962</v>
+      <c r="G142" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11342,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11378,8 +11198,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="7" t="n">
-        <v>1963</v>
+      <c r="G143" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11419,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11455,8 +11275,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="7" t="n">
-        <v>1964</v>
+      <c r="G144" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11496,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11532,8 +11352,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="7" t="n">
-        <v>1965</v>
+      <c r="G145" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11573,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11609,8 +11429,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n">
-        <v>1966</v>
+      <c r="G146" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11650,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11686,8 +11506,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="7" t="n">
-        <v>1967</v>
+      <c r="G147" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11727,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11763,8 +11583,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n">
-        <v>1968</v>
+      <c r="G148" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11804,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11840,8 +11660,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="7" t="n">
-        <v>1969</v>
+      <c r="G149" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11881,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11917,8 +11737,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n">
-        <v>1970</v>
+      <c r="G150" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -11958,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11994,8 +11814,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n">
-        <v>1971</v>
+      <c r="G151" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -12035,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12071,8 +11891,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
-        <v>1972</v>
+      <c r="G152" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12112,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12148,8 +11968,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="7" t="n">
-        <v>1973</v>
+      <c r="G153" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12189,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12225,8 +12045,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="7" t="n">
-        <v>1974</v>
+      <c r="G154" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12266,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12302,8 +12122,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n">
-        <v>1975</v>
+      <c r="G155" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12343,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12379,8 +12199,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n">
-        <v>1976</v>
+      <c r="G156" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12420,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12456,8 +12276,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n">
-        <v>1977</v>
+      <c r="G157" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12497,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12533,8 +12353,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n">
-        <v>1978</v>
+      <c r="G158" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12574,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12610,8 +12430,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n">
-        <v>1979</v>
+      <c r="G159" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12651,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12687,8 +12507,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="7" t="n">
-        <v>1980</v>
+      <c r="G160" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12720,7 +12540,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N160" s="4" t="n"/>
+      <c r="N160" s="6" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12728,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12764,8 +12586,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="7" t="n">
-        <v>1981</v>
+      <c r="G161" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12797,9 +12619,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N161" s="8" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="N161" s="4" t="n"/>
       <c r="O161" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12807,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12843,8 +12663,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="7" t="n">
-        <v>1982</v>
+      <c r="G162" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12884,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12920,8 +12740,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="7" t="n">
-        <v>1983</v>
+      <c r="G163" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -12961,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12997,8 +12817,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="7" t="n">
-        <v>1984</v>
+      <c r="G164" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -13038,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13074,8 +12894,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="7" t="n">
-        <v>1985</v>
+      <c r="G165" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13115,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13151,8 +12971,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="7" t="n">
-        <v>1986</v>
+      <c r="G166" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13184,7 +13004,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N166" s="4" t="n"/>
+      <c r="N166" s="6" t="n">
+        <v>12.3</v>
+      </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13192,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13228,8 +13050,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n">
-        <v>1987</v>
+      <c r="G167" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13261,9 +13083,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N167" s="8" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="N167" s="4" t="n"/>
       <c r="O167" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13271,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13307,8 +13127,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n">
-        <v>1988</v>
+      <c r="G168" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13340,7 +13160,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N168" s="4" t="n"/>
+      <c r="N168" s="6" t="n">
+        <v>7.3</v>
+      </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13348,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13384,8 +13206,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n">
-        <v>1989</v>
+      <c r="G169" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13417,9 +13239,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N169" s="8" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="N169" s="4" t="n"/>
       <c r="O169" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13427,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13463,8 +13283,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n">
-        <v>1990</v>
+      <c r="G170" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13504,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13540,8 +13360,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n">
-        <v>1991</v>
+      <c r="G171" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13573,7 +13393,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N171" s="4" t="n"/>
+      <c r="N171" s="6" t="n">
+        <v>6.9</v>
+      </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13581,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13617,8 +13439,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n">
-        <v>1992</v>
+      <c r="G172" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13650,9 +13472,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N172" s="8" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="N172" s="4" t="n"/>
       <c r="O172" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13660,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13696,8 +13516,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="7" t="n">
-        <v>1993</v>
+      <c r="G173" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13737,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13773,8 +13593,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="7" t="n">
-        <v>1994</v>
+      <c r="G174" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13806,7 +13626,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N174" s="4" t="n"/>
+      <c r="N174" s="6" t="n">
+        <v>15.1</v>
+      </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13814,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13850,8 +13672,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n">
-        <v>1995</v>
+      <c r="G175" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13883,9 +13705,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N175" s="8" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="N175" s="4" t="n"/>
       <c r="O175" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13893,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13929,8 +13749,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="7" t="n">
-        <v>1996</v>
+      <c r="G176" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -13970,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14006,8 +13826,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="7" t="n">
-        <v>1997</v>
+      <c r="G177" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -14039,7 +13859,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N177" s="4" t="n"/>
+      <c r="N177" s="6" t="n">
+        <v>14.9</v>
+      </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14047,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14083,8 +13905,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="7" t="n">
-        <v>1998</v>
+      <c r="G178" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14116,8 +13938,8 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N178" s="8" t="n">
-        <v>14.9</v>
+      <c r="N178" s="6" t="n">
+        <v>16.7</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14126,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14162,8 +13984,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="7" t="n">
-        <v>1999</v>
+      <c r="G179" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14195,9 +14017,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N179" s="8" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="N179" s="4" t="n"/>
       <c r="O179" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14205,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14241,8 +14061,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n">
-        <v>2000</v>
+      <c r="G180" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14274,7 +14094,9 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N180" s="4" t="n"/>
+      <c r="N180" s="6" t="n">
+        <v>14.7</v>
+      </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14282,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14318,8 +14140,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="7" t="n">
-        <v>2001</v>
+      <c r="G181" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14351,8 +14173,8 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N181" s="8" t="n">
-        <v>14.7</v>
+      <c r="N181" s="6" t="n">
+        <v>22.1</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
@@ -14361,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14397,8 +14219,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="7" t="n">
-        <v>2002</v>
+      <c r="G182" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14430,8 +14252,8 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N182" s="8" t="n">
-        <v>22.1</v>
+      <c r="N182" s="6" t="n">
+        <v>27.1</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
@@ -14440,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14476,8 +14298,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="7" t="n">
-        <v>2003</v>
+      <c r="G183" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14509,8 +14331,8 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N183" s="8" t="n">
-        <v>27.1</v>
+      <c r="N183" s="6" t="n">
+        <v>22.8</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
@@ -14519,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14555,8 +14377,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n">
-        <v>2004</v>
+      <c r="G184" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14588,8 +14410,8 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N184" s="8" t="n">
-        <v>22.8</v>
+      <c r="N184" s="6" t="n">
+        <v>18.1</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14598,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14634,8 +14456,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
-        <v>2005</v>
+      <c r="G185" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14667,8 +14489,8 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N185" s="8" t="n">
-        <v>18.1</v>
+      <c r="N185" s="6" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14677,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14713,8 +14535,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n">
-        <v>2006</v>
+      <c r="G186" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14746,9 +14568,7 @@
           <t>Pobreza extrema internacional</t>
         </is>
       </c>
-      <c r="N186" s="8" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="N186" s="4" t="n"/>
       <c r="O186" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14756,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14792,8 +14612,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n">
-        <v>2007</v>
+      <c r="G187" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14833,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14869,8 +14689,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n">
-        <v>2008</v>
+      <c r="G188" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -14910,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14946,8 +14766,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n">
-        <v>2009</v>
+      <c r="G189" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -14987,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15023,8 +14843,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="7" t="n">
-        <v>2010</v>
+      <c r="G190" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -15064,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15100,8 +14920,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="7" t="n">
-        <v>2011</v>
+      <c r="G191" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15141,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15177,8 +14997,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="7" t="n">
-        <v>2012</v>
+      <c r="G192" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15218,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15254,8 +15074,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="7" t="n">
-        <v>2013</v>
+      <c r="G193" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15295,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15331,8 +15151,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="7" t="n">
-        <v>2014</v>
+      <c r="G194" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15372,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15408,8 +15228,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n">
-        <v>2015</v>
+      <c r="G195" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15449,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15485,8 +15305,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="7" t="n">
-        <v>2016</v>
+      <c r="G196" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15526,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15562,8 +15382,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="7" t="n">
-        <v>2017</v>
+      <c r="G197" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15603,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15639,8 +15459,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="7" t="n">
-        <v>2018</v>
+      <c r="G198" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15680,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15716,8 +15536,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="7" t="n">
-        <v>2019</v>
+      <c r="G199" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15757,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15793,8 +15613,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="7" t="n">
-        <v>2020</v>
+      <c r="G200" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15834,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15870,8 +15690,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="7" t="n">
-        <v>2021</v>
+      <c r="G201" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -15911,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15947,8 +15767,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="7" t="n">
-        <v>2022</v>
+      <c r="G202" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -15988,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16024,8 +15844,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="7" t="n">
-        <v>2023</v>
+      <c r="G203" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16065,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16101,8 +15921,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="7" t="n">
-        <v>2024</v>
+      <c r="G204" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16142,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16178,8 +15998,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="7" t="n">
-        <v>2025</v>
+      <c r="G205" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16193,22 +16013,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Pobreza</t>
+          <t>Desigualdad</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>pobreza</t>
+          <t>desigualdad</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>SI.POV.DDAY</t>
+          <t>SI.POV.GINI</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Pobreza extrema internacional</t>
+          <t>Índice de Gini</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16219,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16255,8 +16075,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="7" t="n">
-        <v>1960</v>
+      <c r="G206" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16296,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16332,8 +16152,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="7" t="n">
-        <v>1961</v>
+      <c r="G207" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16373,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16409,8 +16229,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="7" t="n">
-        <v>1962</v>
+      <c r="G208" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16450,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16486,8 +16306,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="7" t="n">
-        <v>1963</v>
+      <c r="G209" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16527,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16563,8 +16383,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="7" t="n">
-        <v>1964</v>
+      <c r="G210" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16604,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16640,8 +16460,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="7" t="n">
-        <v>1965</v>
+      <c r="G211" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16681,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16717,8 +16537,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="7" t="n">
-        <v>1966</v>
+      <c r="G212" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16758,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16794,8 +16614,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="7" t="n">
-        <v>1967</v>
+      <c r="G213" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16835,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16871,8 +16691,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="7" t="n">
-        <v>1968</v>
+      <c r="G214" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -16912,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16948,8 +16768,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="7" t="n">
-        <v>1969</v>
+      <c r="G215" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -16989,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17025,8 +16845,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="7" t="n">
-        <v>1970</v>
+      <c r="G216" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17066,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17102,8 +16922,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="7" t="n">
-        <v>1971</v>
+      <c r="G217" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17143,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17179,8 +16999,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="7" t="n">
-        <v>1972</v>
+      <c r="G218" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17220,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17256,8 +17076,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="7" t="n">
-        <v>1973</v>
+      <c r="G219" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17297,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17333,8 +17153,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="7" t="n">
-        <v>1974</v>
+      <c r="G220" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17374,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17410,8 +17230,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="7" t="n">
-        <v>1975</v>
+      <c r="G221" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17451,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17487,8 +17307,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="7" t="n">
-        <v>1976</v>
+      <c r="G222" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17528,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17564,8 +17384,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="7" t="n">
-        <v>1977</v>
+      <c r="G223" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17605,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17641,8 +17461,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="7" t="n">
-        <v>1978</v>
+      <c r="G224" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17682,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17718,8 +17538,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="7" t="n">
-        <v>1979</v>
+      <c r="G225" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17759,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17795,8 +17615,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="7" t="n">
-        <v>1980</v>
+      <c r="G226" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17828,7 +17648,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N226" s="4" t="n"/>
+      <c r="N226" s="6" t="n">
+        <v>55.6</v>
+      </c>
       <c r="O226" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17836,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17872,8 +17694,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="7" t="n">
-        <v>1981</v>
+      <c r="G227" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -17905,9 +17727,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N227" s="8" t="n">
-        <v>55.6</v>
-      </c>
+      <c r="N227" s="4" t="n"/>
       <c r="O227" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17915,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17951,8 +17771,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="7" t="n">
-        <v>1982</v>
+      <c r="G228" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -17992,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18028,8 +17848,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="7" t="n">
-        <v>1983</v>
+      <c r="G229" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18069,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18105,8 +17925,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="7" t="n">
-        <v>1984</v>
+      <c r="G230" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18146,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18182,8 +18002,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="7" t="n">
-        <v>1985</v>
+      <c r="G231" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18223,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18259,8 +18079,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="7" t="n">
-        <v>1986</v>
+      <c r="G232" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18292,7 +18112,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N232" s="4" t="n"/>
+      <c r="N232" s="6" t="n">
+        <v>53.4</v>
+      </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18300,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18336,8 +18158,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="7" t="n">
-        <v>1987</v>
+      <c r="G233" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18369,9 +18191,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N233" s="8" t="n">
-        <v>53.4</v>
-      </c>
+      <c r="N233" s="4" t="n"/>
       <c r="O233" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18379,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18415,8 +18235,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="7" t="n">
-        <v>1988</v>
+      <c r="G234" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18448,7 +18268,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N234" s="4" t="n"/>
+      <c r="N234" s="6" t="n">
+        <v>43.8</v>
+      </c>
       <c r="O234" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18456,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18492,8 +18314,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="7" t="n">
-        <v>1989</v>
+      <c r="G235" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18525,9 +18347,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N235" s="8" t="n">
-        <v>43.8</v>
-      </c>
+      <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18535,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18571,8 +18391,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="7" t="n">
-        <v>1990</v>
+      <c r="G236" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18612,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18648,8 +18468,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="7" t="n">
-        <v>1991</v>
+      <c r="G237" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18681,7 +18501,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N237" s="4" t="n"/>
+      <c r="N237" s="6" t="n">
+        <v>42.1</v>
+      </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18689,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18725,8 +18547,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="7" t="n">
-        <v>1992</v>
+      <c r="G238" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18758,9 +18580,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N238" s="8" t="n">
-        <v>42.1</v>
-      </c>
+      <c r="N238" s="4" t="n"/>
       <c r="O238" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18768,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18804,8 +18624,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="7" t="n">
-        <v>1993</v>
+      <c r="G239" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18845,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18881,8 +18701,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="7" t="n">
-        <v>1994</v>
+      <c r="G240" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -18914,7 +18734,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n"/>
+      <c r="N240" s="6" t="n">
+        <v>47.2</v>
+      </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18922,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18958,8 +18780,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="7" t="n">
-        <v>1995</v>
+      <c r="G241" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -18991,9 +18813,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N241" s="8" t="n">
-        <v>47.2</v>
-      </c>
+      <c r="N241" s="4" t="n"/>
       <c r="O241" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19001,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19037,8 +18857,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="7" t="n">
-        <v>1996</v>
+      <c r="G242" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19078,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19114,8 +18934,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="7" t="n">
-        <v>1997</v>
+      <c r="G243" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19147,7 +18967,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N243" s="4" t="n"/>
+      <c r="N243" s="5" t="n">
+        <v>48</v>
+      </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19155,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19191,8 +19013,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="7" t="n">
-        <v>1998</v>
+      <c r="G244" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19224,8 +19046,8 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N244" s="7" t="n">
-        <v>48</v>
+      <c r="N244" s="6" t="n">
+        <v>47.7</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19234,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19270,8 +19092,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="7" t="n">
-        <v>1999</v>
+      <c r="G245" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19303,9 +19125,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N245" s="8" t="n">
-        <v>47.7</v>
-      </c>
+      <c r="N245" s="4" t="n"/>
       <c r="O245" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19313,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19349,8 +19169,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="7" t="n">
-        <v>2000</v>
+      <c r="G246" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19382,7 +19202,9 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n"/>
+      <c r="N246" s="6" t="n">
+        <v>47.2</v>
+      </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19390,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19426,8 +19248,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="7" t="n">
-        <v>2001</v>
+      <c r="G247" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19459,8 +19281,8 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N247" s="8" t="n">
-        <v>47.2</v>
+      <c r="N247" s="6" t="n">
+        <v>48.9</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19469,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19505,8 +19327,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="7" t="n">
-        <v>2002</v>
+      <c r="G248" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19538,8 +19360,8 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N248" s="8" t="n">
-        <v>48.9</v>
+      <c r="N248" s="6" t="n">
+        <v>47.9</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19548,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19584,8 +19406,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="7" t="n">
-        <v>2003</v>
+      <c r="G249" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19617,8 +19439,8 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N249" s="8" t="n">
-        <v>47.9</v>
+      <c r="N249" s="6" t="n">
+        <v>47.3</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19627,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19663,8 +19485,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="7" t="n">
-        <v>2004</v>
+      <c r="G250" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19696,8 +19518,8 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N250" s="8" t="n">
-        <v>47.3</v>
+      <c r="N250" s="6" t="n">
+        <v>49.3</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19706,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19742,8 +19564,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="7" t="n">
-        <v>2005</v>
+      <c r="G251" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19775,8 +19597,8 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N251" s="8" t="n">
-        <v>49.3</v>
+      <c r="N251" s="6" t="n">
+        <v>44.7</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19785,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19821,8 +19643,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="7" t="n">
-        <v>2006</v>
+      <c r="G252" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -19854,9 +19676,7 @@
           <t>Índice de Gini</t>
         </is>
       </c>
-      <c r="N252" s="8" t="n">
-        <v>44.7</v>
-      </c>
+      <c r="N252" s="4" t="n"/>
       <c r="O252" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19864,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19900,8 +19720,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="7" t="n">
-        <v>2007</v>
+      <c r="G253" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -19941,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19977,8 +19797,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="7" t="n">
-        <v>2008</v>
+      <c r="G254" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -20018,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20054,8 +19874,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="7" t="n">
-        <v>2009</v>
+      <c r="G255" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20095,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20131,8 +19951,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="7" t="n">
-        <v>2010</v>
+      <c r="G256" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20172,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20208,8 +20028,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="7" t="n">
-        <v>2011</v>
+      <c r="G257" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20249,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20285,8 +20105,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="7" t="n">
-        <v>2012</v>
+      <c r="G258" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20326,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20362,8 +20182,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="7" t="n">
-        <v>2013</v>
+      <c r="G259" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20403,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20439,8 +20259,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="7" t="n">
-        <v>2014</v>
+      <c r="G260" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20480,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20516,8 +20336,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="7" t="n">
-        <v>2015</v>
+      <c r="G261" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20557,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20593,8 +20413,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="7" t="n">
-        <v>2016</v>
+      <c r="G262" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20634,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20670,8 +20490,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="7" t="n">
-        <v>2017</v>
+      <c r="G263" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20711,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20747,8 +20567,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="7" t="n">
-        <v>2018</v>
+      <c r="G264" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20788,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20824,8 +20644,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="7" t="n">
-        <v>2019</v>
+      <c r="G265" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -20865,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20901,8 +20721,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="7" t="n">
-        <v>2020</v>
+      <c r="G266" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -20942,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20978,8 +20798,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="7" t="n">
-        <v>2021</v>
+      <c r="G267" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -21019,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21055,8 +20875,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="7" t="n">
-        <v>2022</v>
+      <c r="G268" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21096,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21132,8 +20952,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="7" t="n">
-        <v>2023</v>
+      <c r="G269" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21173,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21209,8 +21029,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="7" t="n">
-        <v>2024</v>
+      <c r="G270" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21250,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21286,8 +21106,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="7" t="n">
-        <v>2025</v>
+      <c r="G271" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21301,22 +21121,22 @@
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>Desigualdad</t>
+          <t>Pobreza</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>desigualdad</t>
+          <t>pobreza</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>SI.POV.GINI</t>
+          <t>SI.POV.NAHC</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Índice de Gini</t>
+          <t>Pobreza según línea nacional</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21327,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21363,8 +21183,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="7" t="n">
-        <v>1960</v>
+      <c r="G272" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21404,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21440,8 +21260,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="7" t="n">
-        <v>1961</v>
+      <c r="G273" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21481,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21517,8 +21337,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="7" t="n">
-        <v>1962</v>
+      <c r="G274" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21558,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21594,8 +21414,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="7" t="n">
-        <v>1963</v>
+      <c r="G275" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21635,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21671,8 +21491,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="7" t="n">
-        <v>1964</v>
+      <c r="G276" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21712,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21748,8 +21568,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="7" t="n">
-        <v>1965</v>
+      <c r="G277" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21789,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21825,8 +21645,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="7" t="n">
-        <v>1966</v>
+      <c r="G278" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -21866,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21902,8 +21722,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="7" t="n">
-        <v>1967</v>
+      <c r="G279" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -21943,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21979,8 +21799,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="7" t="n">
-        <v>1968</v>
+      <c r="G280" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22020,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22056,8 +21876,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="7" t="n">
-        <v>1969</v>
+      <c r="G281" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22097,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22133,8 +21953,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="7" t="n">
-        <v>1970</v>
+      <c r="G282" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22174,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22210,8 +22030,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="7" t="n">
-        <v>1971</v>
+      <c r="G283" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22251,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22287,8 +22107,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="7" t="n">
-        <v>1972</v>
+      <c r="G284" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22328,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22364,8 +22184,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="7" t="n">
-        <v>1973</v>
+      <c r="G285" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22405,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22441,8 +22261,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="7" t="n">
-        <v>1974</v>
+      <c r="G286" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22482,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22518,8 +22338,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="7" t="n">
-        <v>1975</v>
+      <c r="G287" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22559,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22595,8 +22415,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="7" t="n">
-        <v>1976</v>
+      <c r="G288" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22636,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22672,8 +22492,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="7" t="n">
-        <v>1977</v>
+      <c r="G289" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22713,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22749,8 +22569,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="7" t="n">
-        <v>1978</v>
+      <c r="G290" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22790,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22826,8 +22646,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="7" t="n">
-        <v>1979</v>
+      <c r="G291" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -22867,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22903,8 +22723,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="7" t="n">
-        <v>1980</v>
+      <c r="G292" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -22944,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22980,8 +22800,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="7" t="n">
-        <v>1981</v>
+      <c r="G293" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23021,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23057,8 +22877,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="7" t="n">
-        <v>1982</v>
+      <c r="G294" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23098,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23134,8 +22954,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="7" t="n">
-        <v>1983</v>
+      <c r="G295" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23175,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23211,8 +23031,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="7" t="n">
-        <v>1984</v>
+      <c r="G296" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23252,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23288,8 +23108,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="7" t="n">
-        <v>1985</v>
+      <c r="G297" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23329,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23365,8 +23185,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="7" t="n">
-        <v>1986</v>
+      <c r="G298" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23406,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23442,8 +23262,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="7" t="n">
-        <v>1987</v>
+      <c r="G299" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23483,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23519,8 +23339,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="7" t="n">
-        <v>1988</v>
+      <c r="G300" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23560,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23596,8 +23416,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="7" t="n">
-        <v>1989</v>
+      <c r="G301" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23637,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23673,8 +23493,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="7" t="n">
-        <v>1990</v>
+      <c r="G302" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23714,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23750,8 +23570,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="7" t="n">
-        <v>1991</v>
+      <c r="G303" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23791,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23827,8 +23647,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="7" t="n">
-        <v>1992</v>
+      <c r="G304" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -23868,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23904,8 +23724,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="7" t="n">
-        <v>1993</v>
+      <c r="G305" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -23945,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23981,8 +23801,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="7" t="n">
-        <v>1994</v>
+      <c r="G306" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24022,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24058,8 +23878,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="7" t="n">
-        <v>1995</v>
+      <c r="G307" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24099,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24135,8 +23955,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="7" t="n">
-        <v>1996</v>
+      <c r="G308" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24168,7 +23988,9 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n"/>
+      <c r="N308" s="6" t="n">
+        <v>55.6</v>
+      </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24176,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24212,8 +24034,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="7" t="n">
-        <v>1997</v>
+      <c r="G309" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24245,8 +24067,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N309" s="8" t="n">
-        <v>55.6</v>
+      <c r="N309" s="5" t="n">
+        <v>49</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24255,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24291,8 +24113,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="7" t="n">
-        <v>1998</v>
+      <c r="G310" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24324,8 +24146,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N310" s="7" t="n">
-        <v>49</v>
+      <c r="N310" s="6" t="n">
+        <v>42.8</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24334,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24370,8 +24192,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="7" t="n">
-        <v>1999</v>
+      <c r="G311" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24403,8 +24225,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N311" s="8" t="n">
-        <v>42.8</v>
+      <c r="N311" s="6" t="n">
+        <v>41.6</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24413,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24449,8 +24271,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="7" t="n">
-        <v>2000</v>
+      <c r="G312" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24482,8 +24304,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N312" s="8" t="n">
-        <v>41.6</v>
+      <c r="N312" s="6" t="n">
+        <v>31.1</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24492,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24528,8 +24350,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="7" t="n">
-        <v>2001</v>
+      <c r="G313" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24561,8 +24383,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N313" s="8" t="n">
-        <v>31.1</v>
+      <c r="N313" s="6" t="n">
+        <v>41.1</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24571,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24607,8 +24429,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="7" t="n">
-        <v>2002</v>
+      <c r="G314" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24640,8 +24462,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N314" s="8" t="n">
-        <v>41.1</v>
+      <c r="N314" s="5" t="n">
+        <v>54</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24650,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24686,8 +24508,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="7" t="n">
-        <v>2003</v>
+      <c r="G315" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24719,8 +24541,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N315" s="7" t="n">
-        <v>54</v>
+      <c r="N315" s="6" t="n">
+        <v>53.1</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24729,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24765,8 +24587,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="7" t="n">
-        <v>2004</v>
+      <c r="G316" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24798,8 +24620,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N316" s="8" t="n">
-        <v>53.1</v>
+      <c r="N316" s="6" t="n">
+        <v>42.4</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -24808,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24844,8 +24666,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="7" t="n">
-        <v>2005</v>
+      <c r="G317" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -24877,8 +24699,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N317" s="8" t="n">
-        <v>42.4</v>
+      <c r="N317" s="6" t="n">
+        <v>33.1</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -24887,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24923,8 +24745,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="7" t="n">
-        <v>2006</v>
+      <c r="G318" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -24956,8 +24778,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N318" s="8" t="n">
-        <v>33.1</v>
+      <c r="N318" s="6" t="n">
+        <v>27.5</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -24966,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25002,8 +24824,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="7" t="n">
-        <v>2007</v>
+      <c r="G319" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25035,8 +24857,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N319" s="8" t="n">
-        <v>27.5</v>
+      <c r="N319" s="6" t="n">
+        <v>27.7</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25045,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25081,8 +24903,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="7" t="n">
-        <v>2008</v>
+      <c r="G320" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25114,8 +24936,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N320" s="8" t="n">
-        <v>27.7</v>
+      <c r="N320" s="6" t="n">
+        <v>26.4</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25124,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25160,8 +24982,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="7" t="n">
-        <v>2009</v>
+      <c r="G321" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25193,8 +25015,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N321" s="8" t="n">
-        <v>26.4</v>
+      <c r="N321" s="6" t="n">
+        <v>26.8</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25203,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25239,8 +25061,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="7" t="n">
-        <v>2010</v>
+      <c r="G322" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25272,8 +25094,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N322" s="8" t="n">
-        <v>26.8</v>
+      <c r="N322" s="6" t="n">
+        <v>27.4</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25282,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25318,8 +25140,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="7" t="n">
-        <v>2011</v>
+      <c r="G323" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25351,8 +25173,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N323" s="8" t="n">
-        <v>27.4</v>
+      <c r="N323" s="6" t="n">
+        <v>27.2</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25361,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25397,8 +25219,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="7" t="n">
-        <v>2012</v>
+      <c r="G324" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25430,8 +25252,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N324" s="8" t="n">
-        <v>27.2</v>
+      <c r="N324" s="6" t="n">
+        <v>29.4</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25440,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25476,8 +25298,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="7" t="n">
-        <v>2013</v>
+      <c r="G325" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25509,8 +25331,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N325" s="8" t="n">
-        <v>29.4</v>
+      <c r="N325" s="6" t="n">
+        <v>29.5</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25519,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25555,8 +25377,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="7" t="n">
-        <v>2014</v>
+      <c r="G326" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25588,8 +25410,8 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N326" s="8" t="n">
-        <v>29.5</v>
+      <c r="N326" s="6" t="n">
+        <v>33.1</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
@@ -25598,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25634,8 +25456,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="7" t="n">
-        <v>2015</v>
+      <c r="G327" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25667,9 +25489,7 @@
           <t>Pobreza según línea nacional</t>
         </is>
       </c>
-      <c r="N327" s="8" t="n">
-        <v>33.1</v>
-      </c>
+      <c r="N327" s="4" t="n"/>
       <c r="O327" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25677,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25713,8 +25533,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="7" t="n">
-        <v>2016</v>
+      <c r="G328" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25754,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25790,8 +25610,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="7" t="n">
-        <v>2017</v>
+      <c r="G329" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -25831,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25867,8 +25687,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="7" t="n">
-        <v>2018</v>
+      <c r="G330" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -25908,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25944,8 +25764,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="7" t="n">
-        <v>2019</v>
+      <c r="G331" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -25985,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26021,8 +25841,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="7" t="n">
-        <v>2020</v>
+      <c r="G332" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26062,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26098,8 +25918,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="7" t="n">
-        <v>2021</v>
+      <c r="G333" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26139,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26175,8 +25995,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="7" t="n">
-        <v>2022</v>
+      <c r="G334" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26216,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26252,8 +26072,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="7" t="n">
-        <v>2023</v>
+      <c r="G335" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26293,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26329,8 +26149,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="7" t="n">
-        <v>2024</v>
+      <c r="G336" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26370,87 +26190,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Pobreza y desigualdad</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>pobreza_y_desigualdad</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Pobreza</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>pobreza</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>SI.POV.NAHC</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Pobreza según línea nacional</t>
-        </is>
-      </c>
-      <c r="N337" s="4" t="n"/>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26481,7 +26224,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Pobreza y desigualdad</t>
+          <t>Banco Mundial - Pobreza y desigualdad</t>
         </is>
       </c>
     </row>
@@ -26489,19 +26232,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Organización</t>
         </is>
@@ -26513,7 +26256,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
@@ -26525,35 +26268,35 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Fecha generación</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>331</v>
+      <c r="B11" s="5" t="n">
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
